--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="179">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -376,7 +376,7 @@
 </t>
   </si>
   <si>
-    <t>identifiant du medication définition</t>
+    <t>identifiant du medication</t>
   </si>
   <si>
     <t>fr-lm-medication.classification</t>
@@ -432,7 +432,7 @@
     <t>fr-lm-medication.item.ingredient</t>
   </si>
   <si>
-    <t>Substance active</t>
+    <t>Ingrédient</t>
   </si>
   <si>
     <t>fr-lm-medication.item.ingredient.isActive</t>
@@ -454,13 +454,13 @@
     <t>SMS (2.16.840.1.113883.3.6905.2)</t>
   </si>
   <si>
-    <t>fr-lm-medication.item.ingredient.strength</t>
-  </si>
-  <si>
-    <t>concentration par unité</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.item.ingredient.strength.strength</t>
+    <t>fr-lm-medication.item.ingredient.strengthInfo</t>
+  </si>
+  <si>
+    <t>Concentration de l'ingrédient par unité</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.item.ingredient.strengthInfo.strength</t>
   </si>
   <si>
     <t xml:space="preserve">Ratio
@@ -470,26 +470,39 @@
     <t>numérateur/dénominateur. Ex 100 mg/1 ml ou 500 mg / comprimé.</t>
   </si>
   <si>
-    <t>fr-lm-medication.item.ingredient.strength.basisOfStrengthSubstance</t>
-  </si>
-  <si>
-    <t>Concentration de référence d’une substance</t>
+    <t>fr-lm-medication.item.ingredient.strengthInfo.basisOfStrengthSubstance</t>
+  </si>
+  <si>
+    <t>Substance concernée. code SMS (2.16.840.1.113883.3.6905.2) de la substance active de l’European Medicines Agency (EMA)</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.item.unitOfPresentation</t>
+  </si>
+  <si>
+    <t>Unité de présentation du produit de santé (comprimé, ampoule, tube). En général, le plus petit objet dénombrable du package.
+EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe UOP (Unit of Presentation).</t>
   </si>
   <si>
     <t>fr-lm-medication.item.containedQuantity</t>
+  </si>
+  <si>
+    <t>Quantité de produit par unité (ex : 3 ml / 1 flacon)</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.item.amount</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity
 </t>
   </si>
   <si>
-    <t>quantité pour 1 item</t>
+    <t>Nombre d'unités dans un package (ex : 5 ampoules)</t>
   </si>
   <si>
     <t>fr-lm-medication.item.packageType</t>
   </si>
   <si>
-    <t>Conditionnement primaire (ampoule, bouteille,…) EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe CON (Récipient) =&gt; ampoule, blister.</t>
+    <t>Conditionnement primaire (ampoule, plaquette,…) EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe CON (Récipient).</t>
   </si>
   <si>
     <t>fr-lm-medication.device</t>
@@ -511,7 +524,7 @@
 https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device</t>
   </si>
   <si>
-    <t>Dispositif codé.</t>
+    <t>Code du dispositif</t>
   </si>
   <si>
     <t>fr-lm-medication.characteristic</t>
@@ -857,11 +870,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.7890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.7890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.08203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="58.08203125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -891,7 +904,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="55.7890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="58.08203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -3145,13 +3158,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3219,10 +3232,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3245,13 +3258,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3302,7 +3315,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3319,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3333,7 +3346,7 @@
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3345,7 +3358,7 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>155</v>
@@ -3402,13 +3415,13 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
@@ -3430,7 +3443,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>83</v>
@@ -3445,7 +3458,7 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>157</v>
@@ -3505,7 +3518,7 @@
         <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>83</v>
@@ -3530,10 +3543,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -3545,13 +3558,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>160</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3605,10 +3618,10 @@
         <v>158</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>73</v>
@@ -3619,10 +3632,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3630,10 +3643,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3645,13 +3658,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3702,13 +3715,13 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
@@ -3719,10 +3732,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3745,7 +3758,7 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>164</v>
@@ -3802,7 +3815,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -3833,7 +3846,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3845,13 +3858,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3908,7 +3921,7 @@
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -3919,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3930,7 +3943,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>83</v>
@@ -3945,13 +3958,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4002,10 +4015,10 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>83</v>
@@ -4019,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4045,7 +4058,7 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>171</v>
@@ -4102,7 +4115,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4145,13 +4158,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="M33" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4214,6 +4227,206 @@
         <v>73</v>
       </c>
       <c r="AJ33" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
